--- a/Result/profitability/1324.xlsx
+++ b/Result/profitability/1324.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09999999999999999</v>
+        <v>-0.0925</v>
       </c>
       <c r="N2" t="n">
-        <v>15.0625</v>
+        <v>15.41875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08499999999999999</v>
+        <v>-0.09375</v>
       </c>
       <c r="N3" t="n">
-        <v>14.51</v>
+        <v>15.1275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07125000000000001</v>
+        <v>-0.0575</v>
       </c>
       <c r="N4" t="n">
-        <v>14.38625</v>
+        <v>14.99875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02125</v>
       </c>
       <c r="N5" t="n">
-        <v>14.7075</v>
+        <v>15.6</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03875</v>
+        <v>0.05875000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>15.565</v>
+        <v>16.69875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.065</v>
+        <v>0.08750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>16.75625</v>
+        <v>18.03625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1375</v>
+        <v>0.14875</v>
       </c>
       <c r="N8" t="n">
-        <v>18.425</v>
+        <v>19.095</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>163</v>
+      </c>
+      <c r="D75" t="n">
+        <v>128</v>
+      </c>
+      <c r="E75" t="n">
+        <v>35</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.0975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.9475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.360000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3318885448916411</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.065217391304348</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.140000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4968684759916495</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
